--- a/data/Original datasets/Dataset2.xlsx
+++ b/data/Original datasets/Dataset2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nicol\PHD_Projects\MechanisticAI\MechanisticsAI_julia\data\Original datasets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E7C0E92-D5FD-48F1-BF11-FEC069FC37C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C6C6B07-FC4E-4A06-9A6B-7E98639D455C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-4815" windowWidth="18240" windowHeight="28320" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28830" yWindow="3255" windowWidth="18210" windowHeight="12585" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="STEMI" sheetId="1" r:id="rId1"/>
@@ -15263,7 +15263,7 @@
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="20.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.140625" customWidth="1"/>
+    <col min="3" max="3" width="30" customWidth="1"/>
     <col min="4" max="4" width="18.7109375" customWidth="1"/>
     <col min="5" max="5" width="8.28515625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="12" customWidth="1"/>
@@ -27275,11 +27275,11 @@
         <v>2</v>
       </c>
       <c r="G28" s="17">
-        <v>42357.734722222223</v>
+        <v>42347.734722222223</v>
       </c>
       <c r="H28" s="18">
         <f t="shared" si="5"/>
-        <v>11.234722222223354</v>
+        <v>1.234722222223354</v>
       </c>
       <c r="I28">
         <v>1.4E-2</v>

--- a/data/Original datasets/Dataset2.xlsx
+++ b/data/Original datasets/Dataset2.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28526"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nicol\PHD_Projects\MechanisticAI\MechanisticsAI_julia\data\Original datasets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C6C6B07-FC4E-4A06-9A6B-7E98639D455C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DEDD3CB-4638-4CCC-A440-A7B4E46F0A46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28830" yWindow="3255" windowWidth="18210" windowHeight="12585" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView minimized="1" xWindow="345" yWindow="3870" windowWidth="18210" windowHeight="12585" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="STEMI" sheetId="1" r:id="rId1"/>
@@ -1917,10 +1917,12 @@
       <sz val="16"/>
       <color indexed="8"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="12"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <u/>
@@ -17026,7 +17028,7 @@
     <col min="33" max="33" width="24" customWidth="1"/>
     <col min="35" max="35" width="17" customWidth="1"/>
     <col min="36" max="37" width="27.28515625" customWidth="1"/>
-    <col min="38" max="38" width="11.85546875" customWidth="1"/>
+    <col min="38" max="38" width="29.28515625" customWidth="1"/>
     <col min="40" max="41" width="18.7109375" customWidth="1"/>
     <col min="42" max="42" width="13.7109375" customWidth="1"/>
     <col min="44" max="45" width="20.28515625" customWidth="1"/>
